--- a/public/abc2/material/legal-causas.xlsx
+++ b/public/abc2/material/legal-causas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,12 +413,15 @@
         <v>Estado</v>
       </c>
       <c r="E1" t="str">
+        <v>Última actuación</v>
+      </c>
+      <c r="F1" t="str">
         <v>Próxima fecha</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1234/24</v>
+        <v>1000/24</v>
       </c>
       <c r="B2" t="str">
         <v>Ríos c/ Distribuidora s/ despido</v>
@@ -427,15 +430,18 @@
         <v>Laboral</v>
       </c>
       <c r="D2" t="str">
-        <v>En prueba</v>
+        <v>Inicio</v>
       </c>
       <c r="E2" t="str">
-        <v>10/07/2026</v>
+        <v>01/06/2026</v>
+      </c>
+      <c r="F2" t="str">
+        <v>—</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0876/25</v>
+        <v>1047/25</v>
       </c>
       <c r="B3" t="str">
         <v>Pérez s/ alimentos</v>
@@ -444,15 +450,18 @@
         <v>Familia</v>
       </c>
       <c r="D3" t="str">
-        <v>Audiencia</v>
+        <v>En prueba</v>
       </c>
       <c r="E3" t="str">
-        <v>08/07/2026</v>
+        <v>02/06/2026</v>
+      </c>
+      <c r="F3" t="str">
+        <v>06/07/2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2201/24</v>
+        <v>1094/24</v>
       </c>
       <c r="B4" t="str">
         <v>Sánchez c/ Automotores s/ daños</v>
@@ -461,15 +470,18 @@
         <v>Civil</v>
       </c>
       <c r="D4" t="str">
-        <v>A sentencia</v>
+        <v>Audiencia</v>
       </c>
       <c r="E4" t="str">
-        <v>—</v>
+        <v>03/06/2026</v>
+      </c>
+      <c r="F4" t="str">
+        <v>11/07/2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>0455/25</v>
+        <v>1141/25</v>
       </c>
       <c r="B5" t="str">
         <v>López s/ sucesión</v>
@@ -478,15 +490,338 @@
         <v>Civil</v>
       </c>
       <c r="D5" t="str">
+        <v>A sentencia</v>
+      </c>
+      <c r="E5" t="str">
+        <v>04/06/2026</v>
+      </c>
+      <c r="F5" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1188/24</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Gómez c/ Obra Social s/ amparo</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Contencioso</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Apelación</v>
+      </c>
+      <c r="E6" t="str">
+        <v>05/06/2026</v>
+      </c>
+      <c r="F6" t="str">
+        <v>21/07/2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>1235/25</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Díaz c/ Consorcio s/ daños</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Civil</v>
+      </c>
+      <c r="D7" t="str">
+        <v>En trámite</v>
+      </c>
+      <c r="E7" t="str">
+        <v>06/06/2026</v>
+      </c>
+      <c r="F7" t="str">
+        <v>26/07/2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1282/24</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Ruiz s/ divorcio</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Familia</v>
+      </c>
+      <c r="D8" t="str">
         <v>Inicio</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E8" t="str">
+        <v>07/06/2026</v>
+      </c>
+      <c r="F8" t="str">
         <v>—</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1329/25</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Torres c/ Banco s/ nulidad</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Comercial</v>
+      </c>
+      <c r="D9" t="str">
+        <v>En prueba</v>
+      </c>
+      <c r="E9" t="str">
+        <v>08/06/2026</v>
+      </c>
+      <c r="F9" t="str">
+        <v>09/07/2026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>1376/24</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Vega c/ Empresa s/ despido</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Laboral</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Audiencia</v>
+      </c>
+      <c r="E10" t="str">
+        <v>09/06/2026</v>
+      </c>
+      <c r="F10" t="str">
+        <v>14/07/2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>1423/25</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Núñez s/ tenencia</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Familia</v>
+      </c>
+      <c r="D11" t="str">
+        <v>A sentencia</v>
+      </c>
+      <c r="E11" t="str">
+        <v>10/06/2026</v>
+      </c>
+      <c r="F11" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1470/24</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Ríos c/ Distribuidora s/ despido</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Laboral</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Apelación</v>
+      </c>
+      <c r="E12" t="str">
+        <v>11/06/2026</v>
+      </c>
+      <c r="F12" t="str">
+        <v>24/07/2026</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>1517/25</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Pérez s/ alimentos</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Familia</v>
+      </c>
+      <c r="D13" t="str">
+        <v>En trámite</v>
+      </c>
+      <c r="E13" t="str">
+        <v>12/06/2026</v>
+      </c>
+      <c r="F13" t="str">
+        <v>02/07/2026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>1564/24</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Sánchez c/ Automotores s/ daños</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Civil</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Inicio</v>
+      </c>
+      <c r="E14" t="str">
+        <v>13/06/2026</v>
+      </c>
+      <c r="F14" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>1611/25</v>
+      </c>
+      <c r="B15" t="str">
+        <v>López s/ sucesión</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Civil</v>
+      </c>
+      <c r="D15" t="str">
+        <v>En prueba</v>
+      </c>
+      <c r="E15" t="str">
+        <v>14/06/2026</v>
+      </c>
+      <c r="F15" t="str">
+        <v>12/07/2026</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>1658/24</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Gómez c/ Obra Social s/ amparo</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Contencioso</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Audiencia</v>
+      </c>
+      <c r="E16" t="str">
+        <v>15/06/2026</v>
+      </c>
+      <c r="F16" t="str">
+        <v>17/07/2026</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>1705/25</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Díaz c/ Consorcio s/ daños</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Civil</v>
+      </c>
+      <c r="D17" t="str">
+        <v>A sentencia</v>
+      </c>
+      <c r="E17" t="str">
+        <v>16/06/2026</v>
+      </c>
+      <c r="F17" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>1752/24</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Ruiz s/ divorcio</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Familia</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Apelación</v>
+      </c>
+      <c r="E18" t="str">
+        <v>17/06/2026</v>
+      </c>
+      <c r="F18" t="str">
+        <v>27/07/2026</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>1799/25</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Torres c/ Banco s/ nulidad</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Comercial</v>
+      </c>
+      <c r="D19" t="str">
+        <v>En trámite</v>
+      </c>
+      <c r="E19" t="str">
+        <v>18/06/2026</v>
+      </c>
+      <c r="F19" t="str">
+        <v>05/07/2026</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>1846/24</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Vega c/ Empresa s/ despido</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Laboral</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Inicio</v>
+      </c>
+      <c r="E20" t="str">
+        <v>19/06/2026</v>
+      </c>
+      <c r="F20" t="str">
+        <v>—</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>1893/25</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Núñez s/ tenencia</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Familia</v>
+      </c>
+      <c r="D21" t="str">
+        <v>En prueba</v>
+      </c>
+      <c r="E21" t="str">
+        <v>20/06/2026</v>
+      </c>
+      <c r="F21" t="str">
+        <v>15/07/2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F21"/>
   </ignoredErrors>
 </worksheet>
 </file>